--- a/source/xlsx/A2/unit-3/Deutsch_Heimkehr_A2_U3_L1_v1.0.xlsx
+++ b/source/xlsx/A2/unit-3/Deutsch_Heimkehr_A2_U3_L1_v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Personal Stuff\Docs\GermanCourseApp\deutsch_heimkehr\source\xlsx\A2\unit-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26006988-CF98-4BD3-A98F-56F272FD2442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F7B824-1116-4BFF-9B7C-48894864C288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lesson" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="441">
   <si>
     <t>Practice 4</t>
   </si>
@@ -807,12 +807,6 @@
     <t>Answer</t>
   </si>
   <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>Difficulty</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q01</t>
   </si>
   <si>
@@ -831,12 +825,6 @@
     <t>Die Stelle commonly means a job or position when reading job ads.</t>
   </si>
   <si>
-    <t>Vocabulary</t>
-  </si>
-  <si>
-    <t>Easy</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q02</t>
   </si>
   <si>
@@ -864,9 +852,6 @@
     <t>Ich suche means I am looking for, and Teilzeitstelle means part-time position.</t>
   </si>
   <si>
-    <t>Reading</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q04</t>
   </si>
   <si>
@@ -882,12 +867,6 @@
     <t>Sich bewerben is reflexive: ich bewerbe mich.</t>
   </si>
   <si>
-    <t>Grammar</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q05</t>
   </si>
   <si>
@@ -1005,9 +984,6 @@
     <t>A natural application sentence is: Ich bin zuverlässig und pünktlich.</t>
   </si>
   <si>
-    <t>Writing</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q14</t>
   </si>
   <si>
@@ -1155,9 +1131,6 @@
     <t>Frau Becker asks Sofia to bring her Unterlagen.</t>
   </si>
   <si>
-    <t>Dialogue</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q25</t>
   </si>
   <si>
@@ -1224,9 +1197,6 @@
     <t>Wie hoch ist der Lohn...? is a natural way to ask how high the wage is.</t>
   </si>
   <si>
-    <t>Speaking</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q30</t>
   </si>
   <si>
@@ -1299,9 +1269,6 @@
     <t>In a weil-clause, the conjugated verb moves to the end.</t>
   </si>
   <si>
-    <t>Hard</t>
-  </si>
-  <si>
     <t>A2-U3-L1-Q35</t>
   </si>
   <si>
@@ -1381,9 +1348,6 @@
   </si>
   <si>
     <t>This lesson teaches job ads, applications, interviews, and work availability.</t>
-  </si>
-  <si>
-    <t>Lesson comprehension</t>
   </si>
 </sst>
 </file>
@@ -1649,13 +1613,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4" customHeight="1">
+    <row r="1" spans="1:2" ht="14.45" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="31.65" customHeight="1">
+    <row r="2" spans="1:2" ht="31.7" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="11.4" customHeight="1">
+    <row r="3" spans="1:2" ht="11.45" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -1679,7 +1643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="11.4" customHeight="1">
+    <row r="4" spans="1:2" ht="11.45" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -1687,7 +1651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="11.4" customHeight="1">
+    <row r="5" spans="1:2" ht="11.45" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -1695,7 +1659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.4" customHeight="1">
+    <row r="6" spans="1:2" ht="11.45" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
@@ -1703,7 +1667,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.4" customHeight="1">
+    <row r="7" spans="1:2" ht="11.45" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
@@ -1719,14 +1683,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="4" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="11.4" customHeight="1">
+    <row r="1" spans="1:4" ht="11.45" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -1740,7 +1704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="11.4" customHeight="1">
+    <row r="2" spans="1:4" ht="11.45" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
@@ -1754,7 +1718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="11.4" customHeight="1">
+    <row r="3" spans="1:4" ht="11.45" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
@@ -1768,7 +1732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="11.4" customHeight="1">
+    <row r="4" spans="1:4" ht="11.45" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1782,7 +1746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="11.4" customHeight="1">
+    <row r="5" spans="1:4" ht="11.45" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1796,7 +1760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="11.4" customHeight="1">
+    <row r="6" spans="1:4" ht="11.45" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
@@ -1810,7 +1774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="11.4" customHeight="1">
+    <row r="7" spans="1:4" ht="11.45" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
@@ -1824,7 +1788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="11.4" customHeight="1">
+    <row r="8" spans="1:4" ht="11.45" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
@@ -1838,7 +1802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="11.4" customHeight="1">
+    <row r="9" spans="1:4" ht="11.45" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>47</v>
       </c>
@@ -1852,7 +1816,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="11.4" customHeight="1">
+    <row r="10" spans="1:4" ht="11.45" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
@@ -1866,7 +1830,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="11.4" customHeight="1">
+    <row r="11" spans="1:4" ht="11.45" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1880,7 +1844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="11.4" customHeight="1">
+    <row r="12" spans="1:4" ht="11.45" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
@@ -1894,7 +1858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="11.4" customHeight="1">
+    <row r="13" spans="1:4" ht="11.45" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -1908,7 +1872,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="11.4" customHeight="1">
+    <row r="14" spans="1:4" ht="11.45" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>67</v>
       </c>
@@ -1922,7 +1886,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="11.4" customHeight="1">
+    <row r="15" spans="1:4" ht="11.45" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>71</v>
       </c>
@@ -1936,7 +1900,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="11.4" customHeight="1">
+    <row r="16" spans="1:4" ht="11.45" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1950,7 +1914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="11.4" customHeight="1">
+    <row r="17" spans="1:4" ht="11.45" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>79</v>
       </c>
@@ -1964,7 +1928,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="11.4" customHeight="1">
+    <row r="18" spans="1:4" ht="11.45" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>83</v>
       </c>
@@ -1978,7 +1942,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="11.4" customHeight="1">
+    <row r="19" spans="1:4" ht="11.45" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>85</v>
       </c>
@@ -1992,7 +1956,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="11.4" customHeight="1">
+    <row r="20" spans="1:4" ht="11.45" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>89</v>
       </c>
@@ -2006,7 +1970,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="11.4" customHeight="1">
+    <row r="21" spans="1:4" ht="11.45" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -2020,7 +1984,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="11.4" customHeight="1">
+    <row r="22" spans="1:4" ht="11.45" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>97</v>
       </c>
@@ -2034,7 +1998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="11.4" customHeight="1">
+    <row r="23" spans="1:4" ht="11.45" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>101</v>
       </c>
@@ -2048,7 +2012,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="11.4" customHeight="1">
+    <row r="24" spans="1:4" ht="11.45" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>105</v>
       </c>
@@ -2062,7 +2026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="11.4" customHeight="1">
+    <row r="25" spans="1:4" ht="11.45" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>109</v>
       </c>
@@ -2076,7 +2040,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="11.4" customHeight="1">
+    <row r="26" spans="1:4" ht="11.45" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>113</v>
       </c>
@@ -2090,7 +2054,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="11.4" customHeight="1">
+    <row r="27" spans="1:4" ht="11.45" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>117</v>
       </c>
@@ -2104,7 +2068,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="11.4" customHeight="1">
+    <row r="28" spans="1:4" ht="11.45" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>121</v>
       </c>
@@ -2118,7 +2082,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="11.4" customHeight="1">
+    <row r="29" spans="1:4" ht="11.45" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>125</v>
       </c>
@@ -2132,7 +2096,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="11.4" customHeight="1">
+    <row r="30" spans="1:4" ht="11.45" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>129</v>
       </c>
@@ -2146,7 +2110,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="11.4" customHeight="1">
+    <row r="31" spans="1:4" ht="11.45" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>133</v>
       </c>
@@ -2168,14 +2132,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="11.4" customHeight="1">
+    <row r="1" spans="1:3" ht="11.45" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>137</v>
       </c>
@@ -2186,7 +2150,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="31.65" customHeight="1">
+    <row r="2" spans="1:3" ht="31.7" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>140</v>
       </c>
@@ -2197,7 +2161,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.15" customHeight="1">
+    <row r="3" spans="1:3" ht="21.2" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>143</v>
       </c>
@@ -2208,7 +2172,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.15" customHeight="1">
+    <row r="4" spans="1:3" ht="21.2" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>146</v>
       </c>
@@ -2219,7 +2183,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.15" customHeight="1">
+    <row r="5" spans="1:3" ht="21.2" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>149</v>
       </c>
@@ -2230,7 +2194,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="31.65" customHeight="1">
+    <row r="6" spans="1:3" ht="31.7" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>152</v>
       </c>
@@ -2241,7 +2205,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.15" customHeight="1">
+    <row r="7" spans="1:3" ht="21.2" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>155</v>
       </c>
@@ -2252,7 +2216,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.15" customHeight="1">
+    <row r="8" spans="1:3" ht="21.2" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>158</v>
       </c>
@@ -2263,7 +2227,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.15" customHeight="1">
+    <row r="9" spans="1:3" ht="21.2" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>161</v>
       </c>
@@ -2274,7 +2238,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.15" customHeight="1">
+    <row r="10" spans="1:3" ht="21.2" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>164</v>
       </c>
@@ -2285,7 +2249,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.15" customHeight="1">
+    <row r="11" spans="1:3" ht="21.2" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>167</v>
       </c>
@@ -2296,17 +2260,17 @@
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" ht="15">
       <c r="A12" s="4"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" ht="15">
       <c r="A13" s="4"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" ht="15">
       <c r="A14" s="4"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2319,13 +2283,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="11.4" customHeight="1">
+    <row r="1" spans="1:3" ht="11.45" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>170</v>
       </c>
@@ -2336,7 +2300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.15" customHeight="1">
+    <row r="2" spans="1:3" ht="21.2" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>171</v>
       </c>
@@ -2347,7 +2311,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="11.4" customHeight="1">
+    <row r="3" spans="1:3" ht="11.45" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
@@ -2358,7 +2322,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="11.4" customHeight="1">
+    <row r="4" spans="1:3" ht="11.45" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>171</v>
       </c>
@@ -2369,7 +2333,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="11.4" customHeight="1">
+    <row r="5" spans="1:3" ht="11.45" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>174</v>
       </c>
@@ -2380,7 +2344,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="11.4" customHeight="1">
+    <row r="6" spans="1:3" ht="11.45" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>171</v>
       </c>
@@ -2391,7 +2355,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="11.4" customHeight="1">
+    <row r="7" spans="1:3" ht="11.45" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>174</v>
       </c>
@@ -2402,7 +2366,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="11.4" customHeight="1">
+    <row r="8" spans="1:3" ht="11.45" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>171</v>
       </c>
@@ -2413,7 +2377,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="11.4" customHeight="1">
+    <row r="9" spans="1:3" ht="11.45" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>174</v>
       </c>
@@ -2424,7 +2388,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="11.4" customHeight="1">
+    <row r="10" spans="1:3" ht="11.45" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>171</v>
       </c>
@@ -2435,7 +2399,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="11.4" customHeight="1">
+    <row r="11" spans="1:3" ht="11.45" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>174</v>
       </c>
@@ -2446,7 +2410,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="11.4" customHeight="1">
+    <row r="12" spans="1:3" ht="11.45" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>171</v>
       </c>
@@ -2457,7 +2421,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="11.4" customHeight="1">
+    <row r="13" spans="1:3" ht="11.45" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>174</v>
       </c>
@@ -2468,7 +2432,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="11.4" customHeight="1">
+    <row r="14" spans="1:3" ht="11.45" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>171</v>
       </c>
@@ -2479,7 +2443,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="11.4" customHeight="1">
+    <row r="15" spans="1:3" ht="11.45" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>174</v>
       </c>
@@ -2490,7 +2454,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="11.4" customHeight="1">
+    <row r="16" spans="1:3" ht="11.45" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>171</v>
       </c>
@@ -2501,7 +2465,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="11.4" customHeight="1">
+    <row r="17" spans="1:3" ht="11.45" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>174</v>
       </c>
@@ -2512,7 +2476,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="11.4" customHeight="1">
+    <row r="18" spans="1:3" ht="11.45" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>171</v>
       </c>
@@ -2531,7 +2495,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2539,7 +2503,7 @@
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="11.4" customHeight="1">
+    <row r="1" spans="1:4" ht="11.45" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -2547,7 +2511,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" ht="11.4" customHeight="1">
+    <row r="2" spans="1:4" ht="11.45" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>207</v>
       </c>
@@ -2555,13 +2519,13 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" ht="11.4" customHeight="1">
+    <row r="3" spans="1:4" ht="11.45" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" ht="11.4" customHeight="1">
+    <row r="4" spans="1:4" ht="11.45" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>208</v>
       </c>
@@ -2569,7 +2533,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="11.4" customHeight="1">
+    <row r="5" spans="1:4" ht="11.45" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>209</v>
       </c>
@@ -2577,13 +2541,13 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="11.4" customHeight="1">
+    <row r="6" spans="1:4" ht="11.45" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="31.65" customHeight="1">
+    <row r="7" spans="1:4" ht="31.7" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>210</v>
       </c>
@@ -2597,7 +2561,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="21.15" customHeight="1">
+    <row r="8" spans="1:4" ht="21.2" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>214</v>
       </c>
@@ -2611,7 +2575,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="31.65" customHeight="1">
+    <row r="9" spans="1:4" ht="31.7" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>218</v>
       </c>
@@ -2625,7 +2589,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="21.15" customHeight="1">
+    <row r="10" spans="1:4" ht="21.2" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
@@ -2639,7 +2603,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="21.15" customHeight="1">
+    <row r="11" spans="1:4" ht="21.2" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>225</v>
       </c>
@@ -2653,7 +2617,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21.15" customHeight="1">
+    <row r="12" spans="1:4" ht="21.2" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>229</v>
       </c>
@@ -2667,7 +2631,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="31.65" customHeight="1">
+    <row r="13" spans="1:4" ht="31.7" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>233</v>
       </c>
@@ -2681,7 +2645,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="31.65" customHeight="1">
+    <row r="14" spans="1:4" ht="31.7" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>237</v>
       </c>
@@ -2695,7 +2659,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="21.15" customHeight="1">
+    <row r="15" spans="1:4" ht="21.2" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>241</v>
       </c>
@@ -2709,7 +2673,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="21.15" customHeight="1">
+    <row r="16" spans="1:4" ht="21.2" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>245</v>
       </c>
@@ -2723,7 +2687,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="31.65" customHeight="1">
+    <row r="17" spans="1:4" ht="31.7" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>249</v>
       </c>
@@ -2750,8 +2714,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2759,12 +2723,10 @@
     <col min="4" max="4" width="70" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="65" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="12" max="12" width="90" customWidth="1"/>
+    <col min="10" max="10" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="58.8" customHeight="1">
+    <row r="1" spans="1:10" ht="58.9" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>253</v>
       </c>
@@ -2775,10 +2737,8 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" ht="11.4" customHeight="1">
+    </row>
+    <row r="2" spans="1:10" ht="11.45" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>255</v>
       </c>
@@ -2797,1043 +2757,799 @@
       <c r="F2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>261</v>
-      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="21.15" customHeight="1">
+    </row>
+    <row r="3" spans="1:10" ht="21.2" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>269</v>
-      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="21.15" customHeight="1">
+    </row>
+    <row r="4" spans="1:10" ht="21.2" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="31.7" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="31.65" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:10" ht="11.45" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="11.4" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="21.2" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="G6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:10" ht="11.45" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="21.15" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="21.2" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="11.4" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="21.15" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="11.4" customHeight="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="11.45" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="21.2" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="21.2" customHeight="1">
+      <c r="A12" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="21.15" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E11" s="3" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="11.45" customHeight="1">
+      <c r="A13" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="21.15" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="11.4" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="11.4" customHeight="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="11.45" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="21.15" customHeight="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.2" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="21.15" customHeight="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21.2" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>113</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="11.45" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="11.4" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>121</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A19" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="3" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="11.45" customHeight="1">
+      <c r="A21" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="11.4" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="31.7" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="11.45" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="31.65" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="11.4" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>129</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="11.4" customHeight="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="11.45" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="11.45" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="11.4" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D25" s="3" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A27" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A26" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="3" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A28" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="B28" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A27" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C27" s="3" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="11.45" customHeight="1">
+      <c r="A29" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="11.4" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="11.4" customHeight="1">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="11.45" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="31.65" customHeight="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="31.7" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A34" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B34" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A33" s="3" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A35" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="42.2" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="42.15" customHeight="1">
-      <c r="A36" s="3" t="s">
+    </row>
+    <row r="38" spans="1:6" ht="42.2" customHeight="1">
+      <c r="A38" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B38" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="42.15" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="11.4" customHeight="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="11.45" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="11.4" customHeight="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="11.45" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="31.7" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="21.2" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="31.65" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="21.15" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
